--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102123</v>
+        <v>102126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102123</v>
+        <v>102126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102123</v>
+        <v>102126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102126</v>
+        <v>102127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102126</v>
+        <v>102127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102126</v>
+        <v>102127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80593</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136325967</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136325957</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102127</v>
+        <v>102132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102127</v>
+        <v>102132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102127</v>
+        <v>102132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102132</v>
+        <v>102134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102132</v>
+        <v>102134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102132</v>
+        <v>102134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136325964</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>136325958</v>
       </c>
       <c r="B6" t="n">
-        <v>102134</v>
+        <v>102140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136325962</v>
       </c>
       <c r="B7" t="n">
-        <v>102134</v>
+        <v>102140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136325968</v>
       </c>
       <c r="B8" t="n">
-        <v>102134</v>
+        <v>102140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136325960</v>
       </c>
       <c r="B9" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136325961</v>
       </c>
       <c r="B10" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136325963</v>
       </c>
       <c r="B11" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136325966</v>
       </c>
       <c r="B12" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136325969</v>
       </c>
       <c r="B13" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>136325970</v>
       </c>
       <c r="B14" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136325965</v>
       </c>
       <c r="B16" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>136325959</v>
       </c>
       <c r="B17" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 32345-2026 artfynd.xlsx
+++ b/artfynd/A 32345-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136404446</v>
       </c>
       <c r="B3" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136404445</v>
       </c>
       <c r="B15" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
